--- a/testsource/근무상황목록.masked.xlsx
+++ b/testsource/근무상황목록.masked.xlsx
@@ -250,7 +250,7 @@
   </si>
   <si>
     <t>가다바
-(c111111111)</t>
+(c655423518)</t>
   </si>
   <si>
     <t>영양사</t>
@@ -1746,7 +1746,7 @@
   </si>
   <si>
     <t>가다바
-(c655423518)</t>
+(c111111111)</t>
   </si>
   <si>
     <t>보건과 교재연구 및 교육자료 수집</t>
